--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:48</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:52</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -36,117 +36,117 @@
     <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
+    <t xml:space="preserve">Santo Domingo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Papudo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calle Larga</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Algarrobo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Puchuncaví</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Panquehue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">El Quisco</t>
+  </si>
+  <si>
     <t xml:space="preserve">El Tabo</t>
   </si>
   <si>
-    <t xml:space="preserve">Algarrobo</t>
+    <t xml:space="preserve">Rinconada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Concón</t>
   </si>
   <si>
     <t xml:space="preserve">Zapallar</t>
   </si>
   <si>
-    <t xml:space="preserve">Papudo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Puchuncaví</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santo Domingo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">El Quisco</t>
+    <t xml:space="preserve">Calera</t>
   </si>
   <si>
     <t xml:space="preserve">Quintero</t>
   </si>
   <si>
-    <t xml:space="preserve">Panquehue</t>
+    <t xml:space="preserve">Limache</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Casablanca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Esteban</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Putaendo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Olmué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Llaillay</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cabildo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Santa María</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Antonio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quillota</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Villa Alemana</t>
   </si>
   <si>
     <t xml:space="preserve">Hijuelas</t>
   </si>
   <si>
-    <t xml:space="preserve">Limache</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Concón</t>
+    <t xml:space="preserve">Isla de Pascua</t>
   </si>
   <si>
     <t xml:space="preserve">Cartagena</t>
   </si>
   <si>
-    <t xml:space="preserve">Casablanca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Olmué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rinconada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calle Larga</t>
+    <t xml:space="preserve">Viña del Mar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Ligua</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Catemu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quilpué</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nogales</t>
   </si>
   <si>
     <t xml:space="preserve">La Cruz</t>
   </si>
   <si>
-    <t xml:space="preserve">Villa Alemana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Santa María</t>
-  </si>
-  <si>
-    <t xml:space="preserve">La Ligua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Catemu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Putaendo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Esteban</t>
+    <t xml:space="preserve">Los Andes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">San Felipe</t>
   </si>
   <si>
     <t xml:space="preserve">Juan Fernández</t>
   </si>
   <si>
-    <t xml:space="preserve">San Antonio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Isla de Pascua</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quilpué</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nogales</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quillota</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Viña del Mar</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cabildo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Los Andes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">San Felipe</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Llaillay</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calera</t>
-  </si>
-  <si>
     <t xml:space="preserve">Campo</t>
   </si>
   <si>
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:52</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -586,13 +586,13 @@
         <v>6</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>5605</v>
+        <v>5606</v>
       </c>
       <c r="D2" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>30.46</v>
+        <v>7.02</v>
       </c>
     </row>
     <row r="3">
@@ -603,13 +603,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>5602</v>
+        <v>5403</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>23.9</v>
+        <v>5.28</v>
       </c>
     </row>
     <row r="4">
@@ -620,13 +620,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>5405</v>
+        <v>5302</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>22.46</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="5">
@@ -637,13 +637,13 @@
         <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>5403</v>
+        <v>5602</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>21.39</v>
+        <v>4.73</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>20.23</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="7">
@@ -671,13 +671,13 @@
         <v>11</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>5606</v>
+        <v>5704</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>20.03</v>
+        <v>3.65</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>19.79</v>
+        <v>3.49</v>
       </c>
     </row>
     <row r="9">
@@ -705,13 +705,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>5107</v>
+        <v>5605</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>13.21</v>
+        <v>3.32</v>
       </c>
     </row>
     <row r="10">
@@ -722,13 +722,13 @@
         <v>14</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>5704</v>
+        <v>5303</v>
       </c>
       <c r="D10" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>12.46</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="11">
@@ -739,13 +739,13 @@
         <v>15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>5503</v>
+        <v>5103</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>10.55</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="12">
@@ -756,13 +756,13 @@
         <v>16</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>5802</v>
+        <v>5405</v>
       </c>
       <c r="D12" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>10.34</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="13">
@@ -773,13 +773,13 @@
         <v>17</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>5103</v>
+        <v>5502</v>
       </c>
       <c r="D13" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>10.09</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="14">
@@ -790,13 +790,13 @@
         <v>18</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>5603</v>
+        <v>5107</v>
       </c>
       <c r="D14" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>9.48</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="15">
@@ -807,13 +807,13 @@
         <v>19</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>5102</v>
+        <v>5802</v>
       </c>
       <c r="D15" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>8.25</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="16">
@@ -824,13 +824,13 @@
         <v>20</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>5803</v>
+        <v>5102</v>
       </c>
       <c r="D16" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>7.79</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="17">
@@ -841,13 +841,13 @@
         <v>21</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>5303</v>
+        <v>5304</v>
       </c>
       <c r="D17" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>7.69</v>
+        <v>1.33</v>
       </c>
     </row>
     <row r="18">
@@ -858,13 +858,13 @@
         <v>22</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>5302</v>
+        <v>5705</v>
       </c>
       <c r="D18" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>6.04</v>
+        <v>1.24</v>
       </c>
     </row>
     <row r="19">
@@ -875,13 +875,13 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>5504</v>
+        <v>5803</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>5.88</v>
+        <v>1.19</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>5804</v>
+        <v>5703</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>4.97</v>
+        <v>1.06</v>
       </c>
     </row>
     <row r="21">
@@ -909,13 +909,13 @@
         <v>25</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>5706</v>
+        <v>5402</v>
       </c>
       <c r="D21" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>4.5</v>
+        <v>0.85</v>
       </c>
     </row>
     <row r="22">
@@ -926,13 +926,13 @@
         <v>26</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>5401</v>
+        <v>5706</v>
       </c>
       <c r="D22" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>4.45</v>
+        <v>0.84</v>
       </c>
     </row>
     <row r="23">
@@ -943,13 +943,13 @@
         <v>27</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>5702</v>
+        <v>5601</v>
       </c>
       <c r="D23" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>4.43</v>
+        <v>0.77</v>
       </c>
     </row>
     <row r="24">
@@ -960,13 +960,13 @@
         <v>28</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>5705</v>
+        <v>5501</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>4.43</v>
+        <v>0.76</v>
       </c>
     </row>
     <row r="25">
@@ -977,13 +977,13 @@
         <v>29</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>5304</v>
+        <v>5804</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>4.05</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="26">
@@ -994,13 +994,13 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>5104</v>
+        <v>5503</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>3.27</v>
+        <v>0.23</v>
       </c>
     </row>
     <row r="27">
@@ -1011,13 +1011,13 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>5601</v>
+        <v>5201</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>2.21</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="28">
@@ -1028,13 +1028,13 @@
         <v>32</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>5201</v>
+        <v>5603</v>
       </c>
       <c r="D28" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1.41</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="29">
@@ -1045,13 +1045,13 @@
         <v>33</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>5801</v>
+        <v>5109</v>
       </c>
       <c r="D29" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1.14</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="30">
@@ -1062,13 +1062,13 @@
         <v>34</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>5506</v>
+        <v>5401</v>
       </c>
       <c r="D30" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>0.2</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="31">
@@ -1079,13 +1079,13 @@
         <v>35</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>5501</v>
+        <v>5702</v>
       </c>
       <c r="D31" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.09</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="32">
@@ -1096,13 +1096,13 @@
         <v>36</v>
       </c>
       <c r="C32" s="2" t="n">
-        <v>5109</v>
+        <v>5404</v>
       </c>
       <c r="D32" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="33">
@@ -1113,13 +1113,13 @@
         <v>37</v>
       </c>
       <c r="C33" s="2" t="n">
-        <v>5402</v>
+        <v>5801</v>
       </c>
       <c r="D33" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.76</v>
+        <v>-0.4</v>
       </c>
     </row>
     <row r="34">
@@ -1130,13 +1130,13 @@
         <v>38</v>
       </c>
       <c r="C34" s="2" t="n">
-        <v>5404</v>
+        <v>5506</v>
       </c>
       <c r="D34" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-1.1</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="35">
@@ -1144,16 +1144,16 @@
         <v>5</v>
       </c>
       <c r="B35" s="2" t="s">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="C35" s="2" t="n">
-        <v>5101</v>
+        <v>5504</v>
       </c>
       <c r="D35" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-1.41</v>
+        <v>-0.67</v>
       </c>
     </row>
     <row r="36">
@@ -1161,7 +1161,7 @@
         <v>5</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C36" s="2" t="n">
         <v>5301</v>
@@ -1170,7 +1170,7 @@
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-3.7</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="37">
@@ -1178,16 +1178,16 @@
         <v>5</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>40</v>
+        <v>5</v>
       </c>
       <c r="C37" s="2" t="n">
-        <v>5701</v>
+        <v>5101</v>
       </c>
       <c r="D37" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-4.92</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="38">
@@ -1198,13 +1198,13 @@
         <v>41</v>
       </c>
       <c r="C38" s="2" t="n">
-        <v>5703</v>
+        <v>5701</v>
       </c>
       <c r="D38" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-8.17</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="39">
@@ -1215,13 +1215,13 @@
         <v>42</v>
       </c>
       <c r="C39" s="2" t="n">
-        <v>5502</v>
+        <v>5104</v>
       </c>
       <c r="D39" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-10.37</v>
+        <v>-1.29</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -592,7 +592,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.02</v>
+        <v>70.18</v>
       </c>
     </row>
     <row r="3">
@@ -609,7 +609,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.28</v>
+        <v>52.78</v>
       </c>
     </row>
     <row r="4">
@@ -626,7 +626,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.89</v>
+        <v>48.85</v>
       </c>
     </row>
     <row r="5">
@@ -643,7 +643,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.73</v>
+        <v>47.27</v>
       </c>
     </row>
     <row r="6">
@@ -660,7 +660,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>4.28</v>
+        <v>42.84</v>
       </c>
     </row>
     <row r="7">
@@ -677,7 +677,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>3.65</v>
+        <v>36.53</v>
       </c>
     </row>
     <row r="8">
@@ -694,7 +694,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>3.49</v>
+        <v>34.89</v>
       </c>
     </row>
     <row r="9">
@@ -711,7 +711,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>3.32</v>
+        <v>33.2</v>
       </c>
     </row>
     <row r="10">
@@ -728,7 +728,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>2.92</v>
+        <v>29.15</v>
       </c>
     </row>
     <row r="11">
@@ -745,7 +745,7 @@
         <v>2023</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>2.45</v>
+        <v>24.51</v>
       </c>
     </row>
     <row r="12">
@@ -762,7 +762,7 @@
         <v>2023</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>2.15</v>
+        <v>21.5</v>
       </c>
     </row>
     <row r="13">
@@ -779,7 +779,7 @@
         <v>2023</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>2.14</v>
+        <v>21.39</v>
       </c>
     </row>
     <row r="14">
@@ -796,7 +796,7 @@
         <v>2023</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>2.07</v>
+        <v>20.72</v>
       </c>
     </row>
     <row r="15">
@@ -813,7 +813,7 @@
         <v>2023</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1.9</v>
+        <v>18.98</v>
       </c>
     </row>
     <row r="16">
@@ -830,7 +830,7 @@
         <v>2023</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1.55</v>
+        <v>15.48</v>
       </c>
     </row>
     <row r="17">
@@ -847,7 +847,7 @@
         <v>2023</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1.33</v>
+        <v>13.34</v>
       </c>
     </row>
     <row r="18">
@@ -864,7 +864,7 @@
         <v>2023</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1.24</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="19">
@@ -881,7 +881,7 @@
         <v>2023</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1.19</v>
+        <v>11.85</v>
       </c>
     </row>
     <row r="20">
@@ -898,7 +898,7 @@
         <v>2023</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1.06</v>
+        <v>10.61</v>
       </c>
     </row>
     <row r="21">
@@ -915,7 +915,7 @@
         <v>2023</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>0.85</v>
+        <v>8.48</v>
       </c>
     </row>
     <row r="22">
@@ -932,7 +932,7 @@
         <v>2023</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>0.84</v>
+        <v>8.42</v>
       </c>
     </row>
     <row r="23">
@@ -949,7 +949,7 @@
         <v>2023</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>0.77</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="24">
@@ -966,7 +966,7 @@
         <v>2023</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>0.76</v>
+        <v>7.57</v>
       </c>
     </row>
     <row r="25">
@@ -983,7 +983,7 @@
         <v>2023</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>0.75</v>
+        <v>7.46</v>
       </c>
     </row>
     <row r="26">
@@ -1000,7 +1000,7 @@
         <v>2023</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>0.23</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="27">
@@ -1017,7 +1017,7 @@
         <v>2023</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>0.17</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="28">
@@ -1034,7 +1034,7 @@
         <v>2023</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>0.16</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="29">
@@ -1051,7 +1051,7 @@
         <v>2023</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>0.11</v>
+        <v>1.07</v>
       </c>
     </row>
     <row r="30">
@@ -1068,7 +1068,7 @@
         <v>2023</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>-0.14</v>
+        <v>-1.44</v>
       </c>
     </row>
     <row r="31">
@@ -1085,7 +1085,7 @@
         <v>2023</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>-0.18</v>
+        <v>-1.75</v>
       </c>
     </row>
     <row r="32">
@@ -1102,7 +1102,7 @@
         <v>2023</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>-0.22</v>
+        <v>-2.17</v>
       </c>
     </row>
     <row r="33">
@@ -1119,7 +1119,7 @@
         <v>2023</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>-0.4</v>
+        <v>-4</v>
       </c>
     </row>
     <row r="34">
@@ -1136,7 +1136,7 @@
         <v>2023</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>-0.51</v>
+        <v>-5.08</v>
       </c>
     </row>
     <row r="35">
@@ -1153,7 +1153,7 @@
         <v>2023</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>-0.67</v>
+        <v>-6.71</v>
       </c>
     </row>
     <row r="36">
@@ -1170,7 +1170,7 @@
         <v>2023</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>-0.9</v>
+        <v>-9.02</v>
       </c>
     </row>
     <row r="37">
@@ -1187,7 +1187,7 @@
         <v>2023</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>-0.93</v>
+        <v>-9.29</v>
       </c>
     </row>
     <row r="38">
@@ -1204,7 +1204,7 @@
         <v>2023</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>-1.08</v>
+        <v>-10.75</v>
       </c>
     </row>
     <row r="39">
@@ -1221,7 +1221,7 @@
         <v>2023</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>-1.29</v>
+        <v>-12.85</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:59</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:59</t>
+    <t xml:space="preserve">2026-10-02 13:27</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:27</t>
+    <t xml:space="preserve">2026-10-04 08:18</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_valparaiso.xlsx
@@ -156,7 +156,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-04 08:18</t>
+    <t xml:space="preserve">2026-10-05 08:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
